--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu300000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>609261</t>
+          <t>401477</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>941537</t>
+          <t>540170</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1339019</t>
+          <t>798960</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1708430</t>
+          <t>909582</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1975404</t>
+          <t>1065933</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2296783</t>
+          <t>1230960</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2522372</t>
+          <t>1291522</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2589154</t>
+          <t>1297742</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2599678</t>
+          <t>1302047</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2605511</t>
+          <t>1303575</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2617892</t>
+          <t>1314428</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2639127</t>
+          <t>1324810</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2659509</t>
+          <t>1334810</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2655774</t>
+          <t>1321074</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2622011</t>
+          <t>1301048</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2601512</t>
+          <t>1300575</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2601039</t>
+          <t>1300575</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
